--- a/server/data/reports/Selected_Candidates_2026-10-11.xlsx
+++ b/server/data/reports/Selected_Candidates_2026-10-11.xlsx
@@ -16,7 +16,7 @@
     <t>AvaHire AI - Daily Selected Candidates Report (11-Oct-2026)</t>
   </si>
   <si>
-    <t>Selection Date: 11-Oct-2026  |  Total Selected: 3 Selected Candidates  |  Generated: 12/10/2026, 14:12:51</t>
+    <t>Selection Date: 11-Oct-2026  |  Total Selected: 3 Selected Candidates  |  Generated: 12/10/2026, 19:46:51</t>
   </si>
   <si>
     <t>Sr. No.</t>
